--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567875168</v>
+        <v>46157.93097305777</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097305777</v>
+        <v>46157.93172274619</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172274619</v>
+        <v>46157.93399657017</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399657017</v>
+        <v>46157.93717579758</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717579758</v>
+        <v>46158.28215999718</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28215999718</v>
+        <v>46158.29680696875</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29680696875</v>
+        <v>46158.29814299064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814299064</v>
+        <v>46158.33387016779</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387016779</v>
+        <v>46158.3685672885</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685672885</v>
+        <v>46158.37287513384</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
